--- a/artfynd/A 20429-2025 artfynd.xlsx
+++ b/artfynd/A 20429-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>106410293</v>
       </c>
       <c r="B2" t="n">
-        <v>95514</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,15 +690,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig lopplummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago subsp. selago</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -711,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715618.0899247681</v>
+        <v>715618</v>
       </c>
       <c r="R2" t="n">
-        <v>6352556.775883884</v>
+        <v>6352557</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,19 +743,9 @@
           <t>1990-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 20429-2025 artfynd.xlsx
+++ b/artfynd/A 20429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106410293</v>
       </c>
       <c r="B2" t="n">
-        <v>97446</v>
+        <v>97452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20429-2025 artfynd.xlsx
+++ b/artfynd/A 20429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106410293</v>
       </c>
       <c r="B2" t="n">
-        <v>97452</v>
+        <v>97454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20429-2025 artfynd.xlsx
+++ b/artfynd/A 20429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106410293</v>
       </c>
       <c r="B2" t="n">
-        <v>97454</v>
+        <v>97455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20429-2025 artfynd.xlsx
+++ b/artfynd/A 20429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106410293</v>
       </c>
       <c r="B2" t="n">
-        <v>97455</v>
+        <v>97482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20429-2025 artfynd.xlsx
+++ b/artfynd/A 20429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106410293</v>
       </c>
       <c r="B2" t="n">
-        <v>97482</v>
+        <v>97488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20429-2025 artfynd.xlsx
+++ b/artfynd/A 20429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106410293</v>
       </c>
       <c r="B2" t="n">
-        <v>97488</v>
+        <v>97495</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20429-2025 artfynd.xlsx
+++ b/artfynd/A 20429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106410293</v>
       </c>
       <c r="B2" t="n">
-        <v>97495</v>
+        <v>97499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20429-2025 artfynd.xlsx
+++ b/artfynd/A 20429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106410293</v>
       </c>
       <c r="B2" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20429-2025 artfynd.xlsx
+++ b/artfynd/A 20429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106410293</v>
       </c>
       <c r="B2" t="n">
-        <v>97509</v>
+        <v>97514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20429-2025 artfynd.xlsx
+++ b/artfynd/A 20429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106410293</v>
       </c>
       <c r="B2" t="n">
-        <v>97514</v>
+        <v>97522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20429-2025 artfynd.xlsx
+++ b/artfynd/A 20429-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106410293</v>
+        <v>106501091</v>
       </c>
       <c r="B2" t="n">
-        <v>97522</v>
+        <v>97524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224361</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Burs träsk f.d., Lausmyr S, Gtl</t>
+          <t>Bursträsk, f.d. N-del, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -740,17 +736,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1990-01-01</t>
+          <t>1991-01-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1990-12-31</t>
+          <t>1991-01-11</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>. Två små bestånd Ingrid och Willy Hansson. Koordinat (om den är korrekt) hamnar i Burs socken 35 m från Lau-gränsen. JP</t>
+          <t>. Efter tips av Ingrid och Willy Hansson Burs. Stig H och Sylve Häglund. Riklig sporbildning. Koordinat (om den är korrekt) hamnar i Burs socken 35 m från Lau-gränsen. JP</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,10 +766,116 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Stig Högström, Sylve Häglund</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>106410293</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97522</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Burs träsk f.d., Lausmyr S, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>715618</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6352557</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Burs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1990-01-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1990-12-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>. Två små bestånd Ingrid och Willy Hansson. Koordinat (om den är korrekt) hamnar i Burs socken 35 m från Lau-gränsen. JP</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Via Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Projekt Gotlands Flora</t>
         </is>

--- a/artfynd/A 20429-2025 artfynd.xlsx
+++ b/artfynd/A 20429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106501091</v>
       </c>
       <c r="B2" t="n">
-        <v>97524</v>
+        <v>97977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>106410293</v>
       </c>
       <c r="B3" t="n">
-        <v>97522</v>
+        <v>97975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
